--- a/data/live/BallparkPal_Pitchers_2026-04-12.xlsx
+++ b/data/live/BallparkPal_Pitchers_2026-04-12.xlsx
@@ -586,46 +586,46 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>22.405</v>
+        <v>22.345</v>
       </c>
       <c r="L2" t="n">
-        <v>5.183</v>
+        <v>5.165</v>
       </c>
       <c r="M2" t="n">
-        <v>0.195</v>
+        <v>0.197</v>
       </c>
       <c r="N2" t="n">
-        <v>0.375</v>
+        <v>0.38</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.697</v>
       </c>
       <c r="P2" t="n">
-        <v>0.277</v>
+        <v>0.269</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.917</v>
+        <v>12.102</v>
       </c>
       <c r="R2" t="n">
-        <v>23.315</v>
+        <v>23.525</v>
       </c>
       <c r="S2" t="n">
-        <v>2.773</v>
+        <v>2.79</v>
       </c>
       <c r="T2" t="n">
-        <v>4.951</v>
+        <v>4.902</v>
       </c>
       <c r="U2" t="n">
-        <v>4.601</v>
+        <v>4.713</v>
       </c>
       <c r="V2" t="n">
-        <v>2.041</v>
+        <v>2.028</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.032</v>
       </c>
       <c r="X2" t="n">
-        <v>0.387</v>
+        <v>0.382</v>
       </c>
     </row>
     <row r="3">
@@ -676,46 +676,46 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>22.381</v>
+        <v>22.505</v>
       </c>
       <c r="L3" t="n">
-        <v>5.333</v>
+        <v>5.359</v>
       </c>
       <c r="M3" t="n">
-        <v>0.339</v>
+        <v>0.348</v>
       </c>
       <c r="N3" t="n">
-        <v>0.229</v>
+        <v>0.23</v>
       </c>
       <c r="O3" t="n">
-        <v>0.643</v>
+        <v>0.627</v>
       </c>
       <c r="P3" t="n">
-        <v>0.365</v>
+        <v>0.371</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.329</v>
+        <v>15.733</v>
       </c>
       <c r="R3" t="n">
-        <v>28.341</v>
+        <v>28.982</v>
       </c>
       <c r="S3" t="n">
-        <v>2.124</v>
+        <v>2.184</v>
       </c>
       <c r="T3" t="n">
-        <v>4.42</v>
+        <v>4.49</v>
       </c>
       <c r="U3" t="n">
-        <v>5.074</v>
+        <v>5.294</v>
       </c>
       <c r="V3" t="n">
-        <v>2.142</v>
+        <v>2.092</v>
       </c>
       <c r="W3" t="n">
-        <v>0.617</v>
+        <v>0.618</v>
       </c>
       <c r="X3" t="n">
-        <v>0.198</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="4">
@@ -766,46 +766,46 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>22.035</v>
+        <v>22.289</v>
       </c>
       <c r="L4" t="n">
-        <v>5.332</v>
+        <v>5.421</v>
       </c>
       <c r="M4" t="n">
-        <v>0.174</v>
+        <v>0.18</v>
       </c>
       <c r="N4" t="n">
-        <v>0.378</v>
+        <v>0.372</v>
       </c>
       <c r="O4" t="n">
-        <v>0.696</v>
+        <v>0.681</v>
       </c>
       <c r="P4" t="n">
-        <v>0.327</v>
+        <v>0.347</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.167</v>
+        <v>15.041</v>
       </c>
       <c r="R4" t="n">
-        <v>27.585</v>
+        <v>27.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.272</v>
+        <v>2.23</v>
       </c>
       <c r="T4" t="n">
-        <v>4.183</v>
+        <v>4.227</v>
       </c>
       <c r="U4" t="n">
-        <v>5.35</v>
+        <v>5.119</v>
       </c>
       <c r="V4" t="n">
-        <v>1.969</v>
+        <v>1.886</v>
       </c>
       <c r="W4" t="n">
-        <v>0.908</v>
+        <v>0.835</v>
       </c>
       <c r="X4" t="n">
-        <v>0.645</v>
+        <v>0.639</v>
       </c>
     </row>
     <row r="5">
@@ -856,46 +856,46 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>22.91</v>
+        <v>23.042</v>
       </c>
       <c r="L5" t="n">
-        <v>5.666</v>
+        <v>5.71</v>
       </c>
       <c r="M5" t="n">
-        <v>0.386</v>
+        <v>0.377</v>
       </c>
       <c r="N5" t="n">
-        <v>0.206</v>
+        <v>0.205</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.576</v>
       </c>
       <c r="P5" t="n">
-        <v>0.486</v>
+        <v>0.519</v>
       </c>
       <c r="Q5" t="n">
-        <v>18.375</v>
+        <v>19.326</v>
       </c>
       <c r="R5" t="n">
-        <v>32.797</v>
+        <v>34.33</v>
       </c>
       <c r="S5" t="n">
-        <v>1.773</v>
+        <v>1.754</v>
       </c>
       <c r="T5" t="n">
-        <v>4.409</v>
+        <v>4.244</v>
       </c>
       <c r="U5" t="n">
-        <v>5.619</v>
+        <v>6.041</v>
       </c>
       <c r="V5" t="n">
-        <v>1.658</v>
+        <v>1.821</v>
       </c>
       <c r="W5" t="n">
-        <v>0.373</v>
+        <v>0.398</v>
       </c>
       <c r="X5" t="n">
-        <v>0.661</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -946,46 +946,46 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>23.305</v>
+        <v>23.528</v>
       </c>
       <c r="L6" t="n">
-        <v>5.389</v>
+        <v>5.426</v>
       </c>
       <c r="M6" t="n">
-        <v>0.27</v>
+        <v>0.262</v>
       </c>
       <c r="N6" t="n">
-        <v>0.342</v>
+        <v>0.35</v>
       </c>
       <c r="O6" t="n">
-        <v>0.616</v>
+        <v>0.608</v>
       </c>
       <c r="P6" t="n">
-        <v>0.36</v>
+        <v>0.376</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.528</v>
+        <v>10.49</v>
       </c>
       <c r="R6" t="n">
-        <v>21.928</v>
+        <v>22.085</v>
       </c>
       <c r="S6" t="n">
-        <v>2.521</v>
+        <v>2.573</v>
       </c>
       <c r="T6" t="n">
-        <v>4.912</v>
+        <v>5.041</v>
       </c>
       <c r="U6" t="n">
-        <v>3.421</v>
+        <v>3.482</v>
       </c>
       <c r="V6" t="n">
-        <v>2.583</v>
+        <v>2.626</v>
       </c>
       <c r="W6" t="n">
-        <v>0.521</v>
+        <v>0.496</v>
       </c>
       <c r="X6" t="n">
-        <v>0.652</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="7">
@@ -1036,46 +1036,46 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>21.67</v>
+        <v>21.988</v>
       </c>
       <c r="L7" t="n">
-        <v>4.959</v>
+        <v>5.015</v>
       </c>
       <c r="M7" t="n">
-        <v>0.293</v>
+        <v>0.291</v>
       </c>
       <c r="N7" t="n">
-        <v>0.293</v>
+        <v>0.29</v>
       </c>
       <c r="O7" t="n">
-        <v>0.704</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.253</v>
+        <v>0.262</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.079</v>
+        <v>9.590999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>20.662</v>
+        <v>20.075</v>
       </c>
       <c r="S7" t="n">
-        <v>2.359</v>
+        <v>2.441</v>
       </c>
       <c r="T7" t="n">
-        <v>4.58</v>
+        <v>4.682</v>
       </c>
       <c r="U7" t="n">
-        <v>3.364</v>
+        <v>3.187</v>
       </c>
       <c r="V7" t="n">
-        <v>2.519</v>
+        <v>2.577</v>
       </c>
       <c r="W7" t="n">
-        <v>0.465</v>
+        <v>0.501</v>
       </c>
       <c r="X7" t="n">
-        <v>0.441</v>
+        <v>0.468</v>
       </c>
     </row>
     <row r="8">
@@ -1126,46 +1126,46 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>23.39</v>
+        <v>23.8</v>
       </c>
       <c r="L8" t="n">
-        <v>5.777</v>
+        <v>5.888</v>
       </c>
       <c r="M8" t="n">
-        <v>0.318</v>
+        <v>0.342</v>
       </c>
       <c r="N8" t="n">
-        <v>0.267</v>
+        <v>0.256</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.536</v>
       </c>
       <c r="P8" t="n">
-        <v>0.469</v>
+        <v>0.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>17.016</v>
+        <v>17.47</v>
       </c>
       <c r="R8" t="n">
-        <v>30.777</v>
+        <v>31.579</v>
       </c>
       <c r="S8" t="n">
-        <v>2.139</v>
+        <v>2.136</v>
       </c>
       <c r="T8" t="n">
-        <v>4.78</v>
+        <v>4.843</v>
       </c>
       <c r="U8" t="n">
-        <v>5.36</v>
+        <v>5.422</v>
       </c>
       <c r="V8" t="n">
-        <v>1.433</v>
+        <v>1.409</v>
       </c>
       <c r="W8" t="n">
-        <v>0.775</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>0.307</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="9">
@@ -1216,46 +1216,46 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>18.927</v>
+        <v>18.921</v>
       </c>
       <c r="L9" t="n">
-        <v>4.347</v>
+        <v>4.334</v>
       </c>
       <c r="M9" t="n">
-        <v>0.14</v>
+        <v>0.137</v>
       </c>
       <c r="N9" t="n">
-        <v>0.289</v>
+        <v>0.316</v>
       </c>
       <c r="O9" t="n">
-        <v>0.889</v>
+        <v>0.901</v>
       </c>
       <c r="P9" t="n">
-        <v>0.073</v>
+        <v>0.074</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.543</v>
+        <v>11.496</v>
       </c>
       <c r="R9" t="n">
-        <v>21.483</v>
+        <v>21.429</v>
       </c>
       <c r="S9" t="n">
-        <v>1.906</v>
+        <v>1.955</v>
       </c>
       <c r="T9" t="n">
-        <v>3.764</v>
+        <v>3.723</v>
       </c>
       <c r="U9" t="n">
-        <v>4.343</v>
+        <v>4.391</v>
       </c>
       <c r="V9" t="n">
-        <v>2.353</v>
+        <v>2.411</v>
       </c>
       <c r="W9" t="n">
-        <v>0.435</v>
+        <v>0.47</v>
       </c>
       <c r="X9" t="n">
-        <v>0.236</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="10">
@@ -1306,46 +1306,46 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>23.609</v>
+        <v>24.332</v>
       </c>
       <c r="L10" t="n">
-        <v>6.069</v>
+        <v>6.221</v>
       </c>
       <c r="M10" t="n">
-        <v>0.444</v>
+        <v>0.451</v>
       </c>
       <c r="N10" t="n">
-        <v>0.18</v>
+        <v>0.177</v>
       </c>
       <c r="O10" t="n">
-        <v>0.473</v>
+        <v>0.454</v>
       </c>
       <c r="P10" t="n">
-        <v>0.589</v>
+        <v>0.625</v>
       </c>
       <c r="Q10" t="n">
-        <v>24.873</v>
+        <v>25.555</v>
       </c>
       <c r="R10" t="n">
-        <v>42.14</v>
+        <v>43.41</v>
       </c>
       <c r="S10" t="n">
-        <v>1.538</v>
+        <v>1.632</v>
       </c>
       <c r="T10" t="n">
-        <v>3.612</v>
+        <v>3.837</v>
       </c>
       <c r="U10" t="n">
-        <v>7.843</v>
+        <v>8.145</v>
       </c>
       <c r="V10" t="n">
-        <v>1.788</v>
+        <v>1.768</v>
       </c>
       <c r="W10" t="n">
-        <v>0.609</v>
+        <v>0.67</v>
       </c>
       <c r="X10" t="n">
-        <v>0.365</v>
+        <v>0.379</v>
       </c>
     </row>
     <row r="11">
@@ -1396,46 +1396,46 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>22.569</v>
+        <v>22.965</v>
       </c>
       <c r="L11" t="n">
-        <v>5.358</v>
+        <v>5.405</v>
       </c>
       <c r="M11" t="n">
-        <v>0.177</v>
+        <v>0.17</v>
       </c>
       <c r="N11" t="n">
-        <v>0.461</v>
+        <v>0.465</v>
       </c>
       <c r="O11" t="n">
-        <v>0.639</v>
+        <v>0.642</v>
       </c>
       <c r="P11" t="n">
-        <v>0.365</v>
+        <v>0.387</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.662</v>
+        <v>12.571</v>
       </c>
       <c r="R11" t="n">
-        <v>24.497</v>
+        <v>24.669</v>
       </c>
       <c r="S11" t="n">
-        <v>2.297</v>
+        <v>2.458</v>
       </c>
       <c r="T11" t="n">
-        <v>5.195</v>
+        <v>5.362</v>
       </c>
       <c r="U11" t="n">
-        <v>4.263</v>
+        <v>4.421</v>
       </c>
       <c r="V11" t="n">
-        <v>1.545</v>
+        <v>1.642</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.636</v>
       </c>
       <c r="X11" t="n">
-        <v>0.45</v>
+        <v>0.467</v>
       </c>
     </row>
     <row r="12">
@@ -1486,46 +1486,46 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>22.966</v>
+        <v>23.085</v>
       </c>
       <c r="L12" t="n">
-        <v>5.326</v>
+        <v>5.409</v>
       </c>
       <c r="M12" t="n">
-        <v>0.257</v>
+        <v>0.282</v>
       </c>
       <c r="N12" t="n">
-        <v>0.327</v>
+        <v>0.328</v>
       </c>
       <c r="O12" t="n">
-        <v>0.654</v>
+        <v>0.632</v>
       </c>
       <c r="P12" t="n">
-        <v>0.345</v>
+        <v>0.395</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.856</v>
+        <v>12.516</v>
       </c>
       <c r="R12" t="n">
-        <v>23.658</v>
+        <v>24.733</v>
       </c>
       <c r="S12" t="n">
-        <v>2.549</v>
+        <v>2.408</v>
       </c>
       <c r="T12" t="n">
-        <v>4.892</v>
+        <v>4.804</v>
       </c>
       <c r="U12" t="n">
-        <v>4.135</v>
+        <v>4.153</v>
       </c>
       <c r="V12" t="n">
-        <v>2.326</v>
+        <v>2.327</v>
       </c>
       <c r="W12" t="n">
-        <v>0.706</v>
+        <v>0.68</v>
       </c>
       <c r="X12" t="n">
-        <v>0.53</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="13">
@@ -1576,46 +1576,46 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>22.171</v>
+        <v>22.265</v>
       </c>
       <c r="L13" t="n">
-        <v>5.168</v>
+        <v>5.222</v>
       </c>
       <c r="M13" t="n">
-        <v>0.269</v>
+        <v>0.273</v>
       </c>
       <c r="N13" t="n">
-        <v>0.258</v>
+        <v>0.279</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.672</v>
       </c>
       <c r="P13" t="n">
-        <v>0.299</v>
+        <v>0.321</v>
       </c>
       <c r="Q13" t="n">
-        <v>12.529</v>
+        <v>13.144</v>
       </c>
       <c r="R13" t="n">
-        <v>24.266</v>
+        <v>25.198</v>
       </c>
       <c r="S13" t="n">
-        <v>2.113</v>
+        <v>2.089</v>
       </c>
       <c r="T13" t="n">
-        <v>4.639</v>
+        <v>4.706</v>
       </c>
       <c r="U13" t="n">
-        <v>4.097</v>
+        <v>4.291</v>
       </c>
       <c r="V13" t="n">
-        <v>2.268</v>
+        <v>2.145</v>
       </c>
       <c r="W13" t="n">
-        <v>0.481</v>
+        <v>0.464</v>
       </c>
       <c r="X13" t="n">
-        <v>0.374</v>
+        <v>0.438</v>
       </c>
     </row>
     <row r="14">
@@ -1666,46 +1666,46 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>23.272</v>
+        <v>23.158</v>
       </c>
       <c r="L14" t="n">
-        <v>5.674</v>
+        <v>5.64</v>
       </c>
       <c r="M14" t="n">
-        <v>0.33</v>
+        <v>0.303</v>
       </c>
       <c r="N14" t="n">
-        <v>0.241</v>
+        <v>0.244</v>
       </c>
       <c r="O14" t="n">
-        <v>0.588</v>
+        <v>0.605</v>
       </c>
       <c r="P14" t="n">
-        <v>0.47</v>
+        <v>0.465</v>
       </c>
       <c r="Q14" t="n">
-        <v>22.154</v>
+        <v>22.429</v>
       </c>
       <c r="R14" t="n">
-        <v>38.602</v>
+        <v>39.026</v>
       </c>
       <c r="S14" t="n">
-        <v>1.717</v>
+        <v>1.651</v>
       </c>
       <c r="T14" t="n">
-        <v>3.884</v>
+        <v>3.839</v>
       </c>
       <c r="U14" t="n">
-        <v>7.624</v>
+        <v>7.793</v>
       </c>
       <c r="V14" t="n">
-        <v>2.4</v>
+        <v>2.455</v>
       </c>
       <c r="W14" t="n">
-        <v>0.473</v>
+        <v>0.458</v>
       </c>
       <c r="X14" t="n">
-        <v>0.335</v>
+        <v>0.355</v>
       </c>
     </row>
     <row r="15">
@@ -1756,46 +1756,46 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>21.544</v>
+        <v>21.666</v>
       </c>
       <c r="L15" t="n">
-        <v>5.157</v>
+        <v>5.224</v>
       </c>
       <c r="M15" t="n">
-        <v>0.22</v>
+        <v>0.218</v>
       </c>
       <c r="N15" t="n">
-        <v>0.351</v>
+        <v>0.325</v>
       </c>
       <c r="O15" t="n">
-        <v>0.716</v>
+        <v>0.702</v>
       </c>
       <c r="P15" t="n">
-        <v>0.304</v>
+        <v>0.314</v>
       </c>
       <c r="Q15" t="n">
-        <v>14.309</v>
+        <v>14.497</v>
       </c>
       <c r="R15" t="n">
-        <v>26.344</v>
+        <v>26.546</v>
       </c>
       <c r="S15" t="n">
-        <v>1.915</v>
+        <v>1.848</v>
       </c>
       <c r="T15" t="n">
-        <v>4.25</v>
+        <v>4.214</v>
       </c>
       <c r="U15" t="n">
-        <v>4.695</v>
+        <v>4.618</v>
       </c>
       <c r="V15" t="n">
-        <v>1.979</v>
+        <v>1.934</v>
       </c>
       <c r="W15" t="n">
-        <v>0.512</v>
+        <v>0.498</v>
       </c>
       <c r="X15" t="n">
-        <v>0.429</v>
+        <v>0.413</v>
       </c>
     </row>
     <row r="16">
@@ -1846,46 +1846,46 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>23.398</v>
+        <v>23.395</v>
       </c>
       <c r="L16" t="n">
-        <v>5.839</v>
+        <v>5.842</v>
       </c>
       <c r="M16" t="n">
-        <v>0.376</v>
+        <v>0.382</v>
       </c>
       <c r="N16" t="n">
-        <v>0.222</v>
+        <v>0.223</v>
       </c>
       <c r="O16" t="n">
-        <v>0.537</v>
+        <v>0.528</v>
       </c>
       <c r="P16" t="n">
-        <v>0.502</v>
+        <v>0.501</v>
       </c>
       <c r="Q16" t="n">
-        <v>18.937</v>
+        <v>18.939</v>
       </c>
       <c r="R16" t="n">
-        <v>33.575</v>
+        <v>33.546</v>
       </c>
       <c r="S16" t="n">
-        <v>1.99</v>
+        <v>1.983</v>
       </c>
       <c r="T16" t="n">
-        <v>4.451</v>
+        <v>4.405</v>
       </c>
       <c r="U16" t="n">
-        <v>5.922</v>
+        <v>5.892</v>
       </c>
       <c r="V16" t="n">
-        <v>1.559</v>
+        <v>1.575</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.708</v>
       </c>
       <c r="X16" t="n">
-        <v>0.822</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1936,46 +1936,46 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>21.889</v>
+        <v>21.96</v>
       </c>
       <c r="L17" t="n">
-        <v>5.119</v>
+        <v>5.166</v>
       </c>
       <c r="M17" t="n">
-        <v>0.192</v>
+        <v>0.208</v>
       </c>
       <c r="N17" t="n">
-        <v>0.386</v>
+        <v>0.394</v>
       </c>
       <c r="O17" t="n">
-        <v>0.713</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>0.277</v>
+        <v>0.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.322</v>
+        <v>11.702</v>
       </c>
       <c r="R17" t="n">
-        <v>22.237</v>
+        <v>22.821</v>
       </c>
       <c r="S17" t="n">
-        <v>2.421</v>
+        <v>2.357</v>
       </c>
       <c r="T17" t="n">
-        <v>4.499</v>
+        <v>4.422</v>
       </c>
       <c r="U17" t="n">
-        <v>3.961</v>
+        <v>3.983</v>
       </c>
       <c r="V17" t="n">
-        <v>2.251</v>
+        <v>2.263</v>
       </c>
       <c r="W17" t="n">
-        <v>0.712</v>
+        <v>0.646</v>
       </c>
       <c r="X17" t="n">
-        <v>0.863</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="18">
@@ -2026,46 +2026,46 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>22.374</v>
+        <v>22.571</v>
       </c>
       <c r="L18" t="n">
-        <v>5.583</v>
+        <v>5.637</v>
       </c>
       <c r="M18" t="n">
-        <v>0.382</v>
+        <v>0.392</v>
       </c>
       <c r="N18" t="n">
-        <v>0.212</v>
+        <v>0.204</v>
       </c>
       <c r="O18" t="n">
-        <v>0.585</v>
+        <v>0.571</v>
       </c>
       <c r="P18" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="Q18" t="n">
-        <v>20.824</v>
+        <v>21.648</v>
       </c>
       <c r="R18" t="n">
-        <v>36.034</v>
+        <v>37.272</v>
       </c>
       <c r="S18" t="n">
-        <v>1.84</v>
+        <v>1.898</v>
       </c>
       <c r="T18" t="n">
-        <v>3.745</v>
+        <v>3.762</v>
       </c>
       <c r="U18" t="n">
-        <v>6.899</v>
+        <v>7.295</v>
       </c>
       <c r="V18" t="n">
-        <v>1.934</v>
+        <v>1.956</v>
       </c>
       <c r="W18" t="n">
-        <v>0.749</v>
+        <v>0.78</v>
       </c>
       <c r="X18" t="n">
-        <v>0.581</v>
+        <v>0.539</v>
       </c>
     </row>
     <row r="19">
@@ -2116,46 +2116,46 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>19.464</v>
+        <v>19.462</v>
       </c>
       <c r="L19" t="n">
         <v>4.402</v>
       </c>
       <c r="M19" t="n">
-        <v>0.108</v>
+        <v>0.112</v>
       </c>
       <c r="N19" t="n">
-        <v>0.371</v>
+        <v>0.366</v>
       </c>
       <c r="O19" t="n">
-        <v>0.872</v>
+        <v>0.876</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1</v>
+        <v>0.101</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.087</v>
+        <v>9.090999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>18.208</v>
+        <v>18.231</v>
       </c>
       <c r="S19" t="n">
-        <v>2.182</v>
+        <v>2.23</v>
       </c>
       <c r="T19" t="n">
-        <v>3.747</v>
+        <v>3.831</v>
       </c>
       <c r="U19" t="n">
-        <v>3.5</v>
+        <v>3.546</v>
       </c>
       <c r="V19" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="W19" t="n">
-        <v>0.577</v>
+        <v>0.59</v>
       </c>
       <c r="X19" t="n">
-        <v>0.404</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="20">
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>4.945</v>
+        <v>4.978</v>
       </c>
       <c r="L20" t="n">
-        <v>1.145</v>
+        <v>1.164</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1</v>
+        <v>0.098</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -2224,28 +2224,28 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.066</v>
+        <v>3.239</v>
       </c>
       <c r="R20" t="n">
-        <v>5.564</v>
+        <v>5.788</v>
       </c>
       <c r="S20" t="n">
-        <v>0.458</v>
+        <v>0.473</v>
       </c>
       <c r="T20" t="n">
-        <v>0.989</v>
+        <v>1.004</v>
       </c>
       <c r="U20" t="n">
-        <v>1.167</v>
+        <v>1.239</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.514</v>
       </c>
       <c r="W20" t="n">
-        <v>0.138</v>
+        <v>0.14</v>
       </c>
       <c r="X20" t="n">
-        <v>0.191</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="21">
@@ -2296,46 +2296,46 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>23.498</v>
+        <v>23.374</v>
       </c>
       <c r="L21" t="n">
-        <v>5.589</v>
+        <v>5.542</v>
       </c>
       <c r="M21" t="n">
-        <v>0.37</v>
+        <v>0.329</v>
       </c>
       <c r="N21" t="n">
-        <v>0.217</v>
+        <v>0.222</v>
       </c>
       <c r="O21" t="n">
-        <v>0.576</v>
+        <v>0.614</v>
       </c>
       <c r="P21" t="n">
-        <v>0.429</v>
+        <v>0.41</v>
       </c>
       <c r="Q21" t="n">
-        <v>14.281</v>
+        <v>13.87</v>
       </c>
       <c r="R21" t="n">
-        <v>27.239</v>
+        <v>26.559</v>
       </c>
       <c r="S21" t="n">
-        <v>2.42</v>
+        <v>2.413</v>
       </c>
       <c r="T21" t="n">
-        <v>4.856</v>
+        <v>4.837</v>
       </c>
       <c r="U21" t="n">
-        <v>4.6</v>
+        <v>4.518</v>
       </c>
       <c r="V21" t="n">
-        <v>2.052</v>
+        <v>2.069</v>
       </c>
       <c r="W21" t="n">
-        <v>0.794</v>
+        <v>0.722</v>
       </c>
       <c r="X21" t="n">
-        <v>0.324</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="22">
@@ -2386,46 +2386,46 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>24.993</v>
+        <v>24.991</v>
       </c>
       <c r="L22" t="n">
-        <v>6.121</v>
+        <v>6.127</v>
       </c>
       <c r="M22" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="N22" t="n">
-        <v>0.351</v>
+        <v>0.363</v>
       </c>
       <c r="O22" t="n">
-        <v>0.49</v>
+        <v>0.492</v>
       </c>
       <c r="P22" t="n">
-        <v>0.617</v>
+        <v>0.612</v>
       </c>
       <c r="Q22" t="n">
-        <v>15.389</v>
+        <v>15.242</v>
       </c>
       <c r="R22" t="n">
-        <v>29.411</v>
+        <v>29.125</v>
       </c>
       <c r="S22" t="n">
-        <v>2.085</v>
+        <v>2.082</v>
       </c>
       <c r="T22" t="n">
-        <v>4.78</v>
+        <v>4.875</v>
       </c>
       <c r="U22" t="n">
-        <v>4.364</v>
+        <v>4.286</v>
       </c>
       <c r="V22" t="n">
-        <v>2.14</v>
+        <v>2.008</v>
       </c>
       <c r="W22" t="n">
-        <v>0.449</v>
+        <v>0.437</v>
       </c>
       <c r="X22" t="n">
-        <v>0.37</v>
+        <v>0.385</v>
       </c>
     </row>
     <row r="23">
@@ -2476,46 +2476,46 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>25.051</v>
+        <v>24.981</v>
       </c>
       <c r="L23" t="n">
-        <v>6.284</v>
+        <v>6.313</v>
       </c>
       <c r="M23" t="n">
-        <v>0.334</v>
+        <v>0.35</v>
       </c>
       <c r="N23" t="n">
-        <v>0.271</v>
+        <v>0.264</v>
       </c>
       <c r="O23" t="n">
-        <v>0.488</v>
+        <v>0.474</v>
       </c>
       <c r="P23" t="n">
-        <v>0.658</v>
+        <v>0.663</v>
       </c>
       <c r="Q23" t="n">
-        <v>23.681</v>
+        <v>24.106</v>
       </c>
       <c r="R23" t="n">
-        <v>41.413</v>
+        <v>41.888</v>
       </c>
       <c r="S23" t="n">
-        <v>1.778</v>
+        <v>1.717</v>
       </c>
       <c r="T23" t="n">
-        <v>4.933</v>
+        <v>4.834</v>
       </c>
       <c r="U23" t="n">
-        <v>7.752</v>
+        <v>7.784</v>
       </c>
       <c r="V23" t="n">
-        <v>1.42</v>
+        <v>1.351</v>
       </c>
       <c r="W23" t="n">
-        <v>0.374</v>
+        <v>0.366</v>
       </c>
       <c r="X23" t="n">
-        <v>0.545</v>
+        <v>0.556</v>
       </c>
     </row>
     <row r="24">
@@ -2566,46 +2566,46 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>22.155</v>
+        <v>22.276</v>
       </c>
       <c r="L24" t="n">
-        <v>5.151</v>
+        <v>5.178</v>
       </c>
       <c r="M24" t="n">
-        <v>0.254</v>
+        <v>0.246</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3</v>
+        <v>0.298</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.705</v>
       </c>
       <c r="P24" t="n">
-        <v>0.322</v>
+        <v>0.34</v>
       </c>
       <c r="Q24" t="n">
-        <v>16.904</v>
+        <v>16.693</v>
       </c>
       <c r="R24" t="n">
-        <v>31.024</v>
+        <v>30.787</v>
       </c>
       <c r="S24" t="n">
-        <v>2.032</v>
+        <v>2.029</v>
       </c>
       <c r="T24" t="n">
-        <v>3.976</v>
+        <v>4.095</v>
       </c>
       <c r="U24" t="n">
-        <v>6.286</v>
+        <v>6.168</v>
       </c>
       <c r="V24" t="n">
-        <v>3.041</v>
+        <v>2.956</v>
       </c>
       <c r="W24" t="n">
-        <v>0.444</v>
+        <v>0.402</v>
       </c>
       <c r="X24" t="n">
-        <v>0.514</v>
+        <v>0.523</v>
       </c>
     </row>
     <row r="25">
@@ -2656,46 +2656,46 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>24.248</v>
+        <v>24.37</v>
       </c>
       <c r="L25" t="n">
-        <v>5.837</v>
+        <v>5.882</v>
       </c>
       <c r="M25" t="n">
-        <v>0.306</v>
+        <v>0.301</v>
       </c>
       <c r="N25" t="n">
-        <v>0.286</v>
+        <v>0.283</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>0.486</v>
+        <v>0.51</v>
       </c>
       <c r="Q25" t="n">
-        <v>18.474</v>
+        <v>17.627</v>
       </c>
       <c r="R25" t="n">
-        <v>33.556</v>
+        <v>32.403</v>
       </c>
       <c r="S25" t="n">
-        <v>2.175</v>
+        <v>2.118</v>
       </c>
       <c r="T25" t="n">
-        <v>4.533</v>
+        <v>4.667</v>
       </c>
       <c r="U25" t="n">
-        <v>6.264</v>
+        <v>5.755</v>
       </c>
       <c r="V25" t="n">
-        <v>2.301</v>
+        <v>2.206</v>
       </c>
       <c r="W25" t="n">
-        <v>0.697</v>
+        <v>0.61</v>
       </c>
       <c r="X25" t="n">
-        <v>0.593</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="26">
@@ -2746,46 +2746,46 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>22.743</v>
+        <v>22.787</v>
       </c>
       <c r="L26" t="n">
-        <v>5.262</v>
+        <v>5.318</v>
       </c>
       <c r="M26" t="n">
-        <v>0.273</v>
+        <v>0.264</v>
       </c>
       <c r="N26" t="n">
-        <v>0.267</v>
+        <v>0.271</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="P26" t="n">
-        <v>0.285</v>
+        <v>0.311</v>
       </c>
       <c r="Q26" t="n">
-        <v>11.714</v>
+        <v>11.954</v>
       </c>
       <c r="R26" t="n">
-        <v>23.007</v>
+        <v>23.371</v>
       </c>
       <c r="S26" t="n">
-        <v>3.008</v>
+        <v>2.95</v>
       </c>
       <c r="T26" t="n">
-        <v>5.365</v>
+        <v>5.319</v>
       </c>
       <c r="U26" t="n">
-        <v>4.488</v>
+        <v>4.478</v>
       </c>
       <c r="V26" t="n">
-        <v>1.623</v>
+        <v>1.583</v>
       </c>
       <c r="W26" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
-        <v>0.369</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="27">
@@ -2836,46 +2836,46 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>21.198</v>
+        <v>21.401</v>
       </c>
       <c r="L27" t="n">
-        <v>4.614</v>
+        <v>4.702</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2</v>
+        <v>0.207</v>
       </c>
       <c r="N27" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="O27" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.793</v>
       </c>
       <c r="P27" t="n">
-        <v>0.164</v>
+        <v>0.183</v>
       </c>
       <c r="Q27" t="n">
-        <v>11.475</v>
+        <v>12.138</v>
       </c>
       <c r="R27" t="n">
-        <v>22.928</v>
+        <v>23.894</v>
       </c>
       <c r="S27" t="n">
-        <v>2.849</v>
+        <v>2.79</v>
       </c>
       <c r="T27" t="n">
-        <v>4.43</v>
+        <v>4.362</v>
       </c>
       <c r="U27" t="n">
-        <v>5.259</v>
+        <v>5.394</v>
       </c>
       <c r="V27" t="n">
-        <v>3.118</v>
+        <v>3.104</v>
       </c>
       <c r="W27" t="n">
-        <v>0.89</v>
+        <v>0.859</v>
       </c>
       <c r="X27" t="n">
-        <v>0.431</v>
+        <v>0.432</v>
       </c>
     </row>
     <row r="28">
@@ -2926,46 +2926,46 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>23.041</v>
+        <v>23.098</v>
       </c>
       <c r="L28" t="n">
-        <v>5.377</v>
+        <v>5.397</v>
       </c>
       <c r="M28" t="n">
-        <v>0.296</v>
+        <v>0.301</v>
       </c>
       <c r="N28" t="n">
-        <v>0.294</v>
+        <v>0.301</v>
       </c>
       <c r="O28" t="n">
-        <v>0.63</v>
+        <v>0.617</v>
       </c>
       <c r="P28" t="n">
-        <v>0.398</v>
+        <v>0.416</v>
       </c>
       <c r="Q28" t="n">
-        <v>13.224</v>
+        <v>13.314</v>
       </c>
       <c r="R28" t="n">
-        <v>25.933</v>
+        <v>26.115</v>
       </c>
       <c r="S28" t="n">
-        <v>2.214</v>
+        <v>2.25</v>
       </c>
       <c r="T28" t="n">
-        <v>4.647</v>
+        <v>4.69</v>
       </c>
       <c r="U28" t="n">
-        <v>4.359</v>
+        <v>4.403</v>
       </c>
       <c r="V28" t="n">
-        <v>2.612</v>
+        <v>2.563</v>
       </c>
       <c r="W28" t="n">
-        <v>0.373</v>
+        <v>0.399</v>
       </c>
       <c r="X28" t="n">
-        <v>0.434</v>
+        <v>0.439</v>
       </c>
     </row>
     <row r="29">
@@ -3016,46 +3016,46 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>23.432</v>
+        <v>23.777</v>
       </c>
       <c r="L29" t="n">
-        <v>5.368</v>
+        <v>5.485</v>
       </c>
       <c r="M29" t="n">
-        <v>0.263</v>
+        <v>0.272</v>
       </c>
       <c r="N29" t="n">
-        <v>0.317</v>
+        <v>0.32</v>
       </c>
       <c r="O29" t="n">
-        <v>0.64</v>
+        <v>0.612</v>
       </c>
       <c r="P29" t="n">
-        <v>0.365</v>
+        <v>0.385</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>13.407</v>
       </c>
       <c r="R29" t="n">
-        <v>25.8</v>
+        <v>26.441</v>
       </c>
       <c r="S29" t="n">
-        <v>2.361</v>
+        <v>2.4</v>
       </c>
       <c r="T29" t="n">
-        <v>5.048</v>
+        <v>5.103</v>
       </c>
       <c r="U29" t="n">
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="V29" t="n">
-        <v>2.584</v>
+        <v>2.524</v>
       </c>
       <c r="W29" t="n">
-        <v>0.386</v>
+        <v>0.445</v>
       </c>
       <c r="X29" t="n">
-        <v>0.335</v>
+        <v>0.352</v>
       </c>
     </row>
     <row r="30">
@@ -3106,46 +3106,46 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>24.742</v>
+        <v>24.776</v>
       </c>
       <c r="L30" t="n">
-        <v>5.98</v>
+        <v>5.982</v>
       </c>
       <c r="M30" t="n">
-        <v>0.35</v>
+        <v>0.362</v>
       </c>
       <c r="N30" t="n">
-        <v>0.272</v>
+        <v>0.278</v>
       </c>
       <c r="O30" t="n">
-        <v>0.515</v>
+        <v>0.504</v>
       </c>
       <c r="P30" t="n">
-        <v>0.552</v>
+        <v>0.547</v>
       </c>
       <c r="Q30" t="n">
-        <v>20.309</v>
+        <v>20.552</v>
       </c>
       <c r="R30" t="n">
-        <v>36.555</v>
+        <v>36.976</v>
       </c>
       <c r="S30" t="n">
         <v>2.104</v>
       </c>
       <c r="T30" t="n">
-        <v>4.956</v>
+        <v>4.964</v>
       </c>
       <c r="U30" t="n">
-        <v>6.874</v>
+        <v>6.994</v>
       </c>
       <c r="V30" t="n">
-        <v>1.94</v>
+        <v>2.013</v>
       </c>
       <c r="W30" t="n">
-        <v>0.536</v>
+        <v>0.545</v>
       </c>
       <c r="X30" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="31">
@@ -3196,46 +3196,46 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>23.309</v>
+        <v>23.302</v>
       </c>
       <c r="L31" t="n">
-        <v>5.545</v>
+        <v>5.519</v>
       </c>
       <c r="M31" t="n">
-        <v>0.267</v>
+        <v>0.269</v>
       </c>
       <c r="N31" t="n">
-        <v>0.355</v>
+        <v>0.374</v>
       </c>
       <c r="O31" t="n">
-        <v>0.605</v>
+        <v>0.594</v>
       </c>
       <c r="P31" t="n">
-        <v>0.434</v>
+        <v>0.431</v>
       </c>
       <c r="Q31" t="n">
-        <v>14.647</v>
+        <v>14.351</v>
       </c>
       <c r="R31" t="n">
-        <v>27.755</v>
+        <v>27.374</v>
       </c>
       <c r="S31" t="n">
-        <v>2.342</v>
+        <v>2.348</v>
       </c>
       <c r="T31" t="n">
-        <v>4.869</v>
+        <v>4.849</v>
       </c>
       <c r="U31" t="n">
-        <v>4.937</v>
+        <v>4.84</v>
       </c>
       <c r="V31" t="n">
-        <v>1.96</v>
+        <v>2.065</v>
       </c>
       <c r="W31" t="n">
-        <v>0.604</v>
+        <v>0.606</v>
       </c>
       <c r="X31" t="n">
-        <v>0.402</v>
+        <v>0.413</v>
       </c>
     </row>
   </sheetData>

--- a/data/live/BallparkPal_Pitchers_2026-04-12.xlsx
+++ b/data/live/BallparkPal_Pitchers_2026-04-12.xlsx
@@ -2746,46 +2746,46 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>22.787</v>
+        <v>22.819</v>
       </c>
       <c r="L26" t="n">
-        <v>5.318</v>
+        <v>5.321</v>
       </c>
       <c r="M26" t="n">
-        <v>0.264</v>
+        <v>0.261</v>
       </c>
       <c r="N26" t="n">
-        <v>0.271</v>
+        <v>0.295</v>
       </c>
       <c r="O26" t="n">
-        <v>0.67</v>
+        <v>0.658</v>
       </c>
       <c r="P26" t="n">
-        <v>0.311</v>
+        <v>0.318</v>
       </c>
       <c r="Q26" t="n">
-        <v>11.954</v>
+        <v>12.138</v>
       </c>
       <c r="R26" t="n">
-        <v>23.371</v>
+        <v>23.699</v>
       </c>
       <c r="S26" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="T26" t="n">
-        <v>5.319</v>
+        <v>5.287</v>
       </c>
       <c r="U26" t="n">
-        <v>4.478</v>
+        <v>4.494</v>
       </c>
       <c r="V26" t="n">
-        <v>1.583</v>
+        <v>1.637</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X26" t="n">
-        <v>0.372</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="27">
@@ -2836,46 +2836,46 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>21.401</v>
+        <v>21.52</v>
       </c>
       <c r="L27" t="n">
-        <v>4.702</v>
+        <v>4.778</v>
       </c>
       <c r="M27" t="n">
-        <v>0.207</v>
+        <v>0.225</v>
       </c>
       <c r="N27" t="n">
-        <v>0.281</v>
+        <v>0.265</v>
       </c>
       <c r="O27" t="n">
-        <v>0.793</v>
+        <v>0.799</v>
       </c>
       <c r="P27" t="n">
-        <v>0.183</v>
+        <v>0.199</v>
       </c>
       <c r="Q27" t="n">
-        <v>12.138</v>
+        <v>13.042</v>
       </c>
       <c r="R27" t="n">
-        <v>23.894</v>
+        <v>25.215</v>
       </c>
       <c r="S27" t="n">
-        <v>2.79</v>
+        <v>2.556</v>
       </c>
       <c r="T27" t="n">
-        <v>4.362</v>
+        <v>4.316</v>
       </c>
       <c r="U27" t="n">
-        <v>5.394</v>
+        <v>5.467</v>
       </c>
       <c r="V27" t="n">
-        <v>3.104</v>
+        <v>3.074</v>
       </c>
       <c r="W27" t="n">
-        <v>0.859</v>
+        <v>0.717</v>
       </c>
       <c r="X27" t="n">
-        <v>0.432</v>
+        <v>0.487</v>
       </c>
     </row>
     <row r="28">

--- a/data/live/BallparkPal_Pitchers_2026-04-12.xlsx
+++ b/data/live/BallparkPal_Pitchers_2026-04-12.xlsx
@@ -586,46 +586,46 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>22.345</v>
+        <v>22.269</v>
       </c>
       <c r="L2" t="n">
-        <v>5.165</v>
+        <v>5.179</v>
       </c>
       <c r="M2" t="n">
-        <v>0.197</v>
+        <v>0.187</v>
       </c>
       <c r="N2" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O2" t="n">
-        <v>0.697</v>
+        <v>0.705</v>
       </c>
       <c r="P2" t="n">
-        <v>0.269</v>
+        <v>0.279</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.102</v>
+        <v>12.421</v>
       </c>
       <c r="R2" t="n">
-        <v>23.525</v>
+        <v>23.921</v>
       </c>
       <c r="S2" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="T2" t="n">
-        <v>4.902</v>
+        <v>4.841</v>
       </c>
       <c r="U2" t="n">
-        <v>4.713</v>
+        <v>4.779</v>
       </c>
       <c r="V2" t="n">
-        <v>2.028</v>
+        <v>1.961</v>
       </c>
       <c r="W2" t="n">
-        <v>1.032</v>
+        <v>1.057</v>
       </c>
       <c r="X2" t="n">
-        <v>0.382</v>
+        <v>0.293</v>
       </c>
     </row>
     <row r="3">
@@ -676,46 +676,46 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>22.505</v>
+        <v>22.519</v>
       </c>
       <c r="L3" t="n">
-        <v>5.359</v>
+        <v>5.404</v>
       </c>
       <c r="M3" t="n">
-        <v>0.348</v>
+        <v>0.362</v>
       </c>
       <c r="N3" t="n">
-        <v>0.23</v>
+        <v>0.223</v>
       </c>
       <c r="O3" t="n">
-        <v>0.627</v>
+        <v>0.61</v>
       </c>
       <c r="P3" t="n">
-        <v>0.371</v>
+        <v>0.396</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.733</v>
+        <v>16.325</v>
       </c>
       <c r="R3" t="n">
-        <v>28.982</v>
+        <v>29.848</v>
       </c>
       <c r="S3" t="n">
-        <v>2.184</v>
+        <v>2.055</v>
       </c>
       <c r="T3" t="n">
-        <v>4.49</v>
+        <v>4.409</v>
       </c>
       <c r="U3" t="n">
-        <v>5.294</v>
+        <v>5.349</v>
       </c>
       <c r="V3" t="n">
-        <v>2.092</v>
+        <v>2.067</v>
       </c>
       <c r="W3" t="n">
-        <v>0.618</v>
+        <v>0.591</v>
       </c>
       <c r="X3" t="n">
-        <v>0.23</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="4">
@@ -1846,46 +1846,46 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>23.395</v>
+        <v>23.456</v>
       </c>
       <c r="L16" t="n">
-        <v>5.842</v>
+        <v>5.854</v>
       </c>
       <c r="M16" t="n">
-        <v>0.382</v>
+        <v>0.364</v>
       </c>
       <c r="N16" t="n">
-        <v>0.223</v>
+        <v>0.225</v>
       </c>
       <c r="O16" t="n">
-        <v>0.528</v>
+        <v>0.531</v>
       </c>
       <c r="P16" t="n">
-        <v>0.501</v>
+        <v>0.504</v>
       </c>
       <c r="Q16" t="n">
-        <v>18.939</v>
+        <v>18.876</v>
       </c>
       <c r="R16" t="n">
-        <v>33.546</v>
+        <v>33.504</v>
       </c>
       <c r="S16" t="n">
-        <v>1.983</v>
+        <v>1.978</v>
       </c>
       <c r="T16" t="n">
-        <v>4.405</v>
+        <v>4.411</v>
       </c>
       <c r="U16" t="n">
-        <v>5.892</v>
+        <v>5.891</v>
       </c>
       <c r="V16" t="n">
-        <v>1.575</v>
+        <v>1.598</v>
       </c>
       <c r="W16" t="n">
-        <v>0.708</v>
+        <v>0.7</v>
       </c>
       <c r="X16" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.859</v>
       </c>
     </row>
     <row r="17">
@@ -1936,46 +1936,46 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>21.96</v>
+        <v>22.156</v>
       </c>
       <c r="L17" t="n">
-        <v>5.166</v>
+        <v>5.228</v>
       </c>
       <c r="M17" t="n">
-        <v>0.208</v>
+        <v>0.206</v>
       </c>
       <c r="N17" t="n">
-        <v>0.394</v>
+        <v>0.38</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3</v>
+        <v>0.313</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.702</v>
+        <v>11.822</v>
       </c>
       <c r="R17" t="n">
-        <v>22.821</v>
+        <v>23.077</v>
       </c>
       <c r="S17" t="n">
-        <v>2.357</v>
+        <v>2.39</v>
       </c>
       <c r="T17" t="n">
-        <v>4.422</v>
+        <v>4.488</v>
       </c>
       <c r="U17" t="n">
-        <v>3.983</v>
+        <v>4.025</v>
       </c>
       <c r="V17" t="n">
-        <v>2.263</v>
+        <v>2.246</v>
       </c>
       <c r="W17" t="n">
-        <v>0.646</v>
+        <v>0.676</v>
       </c>
       <c r="X17" t="n">
-        <v>0.843</v>
+        <v>0.884</v>
       </c>
     </row>
     <row r="18">
@@ -2926,46 +2926,46 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>23.098</v>
+        <v>23.047</v>
       </c>
       <c r="L28" t="n">
-        <v>5.397</v>
+        <v>5.381</v>
       </c>
       <c r="M28" t="n">
-        <v>0.301</v>
+        <v>0.307</v>
       </c>
       <c r="N28" t="n">
-        <v>0.301</v>
+        <v>0.292</v>
       </c>
       <c r="O28" t="n">
-        <v>0.617</v>
+        <v>0.619</v>
       </c>
       <c r="P28" t="n">
-        <v>0.416</v>
+        <v>0.413</v>
       </c>
       <c r="Q28" t="n">
-        <v>13.314</v>
+        <v>13.218</v>
       </c>
       <c r="R28" t="n">
-        <v>26.115</v>
+        <v>25.952</v>
       </c>
       <c r="S28" t="n">
-        <v>2.25</v>
+        <v>2.221</v>
       </c>
       <c r="T28" t="n">
-        <v>4.69</v>
+        <v>4.699</v>
       </c>
       <c r="U28" t="n">
-        <v>4.403</v>
+        <v>4.327</v>
       </c>
       <c r="V28" t="n">
-        <v>2.563</v>
+        <v>2.536</v>
       </c>
       <c r="W28" t="n">
-        <v>0.399</v>
+        <v>0.376</v>
       </c>
       <c r="X28" t="n">
-        <v>0.439</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="29">
@@ -3016,46 +3016,46 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>23.777</v>
+        <v>23.939</v>
       </c>
       <c r="L29" t="n">
-        <v>5.485</v>
+        <v>5.525</v>
       </c>
       <c r="M29" t="n">
-        <v>0.272</v>
+        <v>0.261</v>
       </c>
       <c r="N29" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="O29" t="n">
-        <v>0.612</v>
+        <v>0.618</v>
       </c>
       <c r="P29" t="n">
-        <v>0.385</v>
+        <v>0.402</v>
       </c>
       <c r="Q29" t="n">
-        <v>13.407</v>
+        <v>14.641</v>
       </c>
       <c r="R29" t="n">
-        <v>26.441</v>
+        <v>28.355</v>
       </c>
       <c r="S29" t="n">
-        <v>2.4</v>
+        <v>2.413</v>
       </c>
       <c r="T29" t="n">
-        <v>5.103</v>
+        <v>5.118</v>
       </c>
       <c r="U29" t="n">
-        <v>4.67</v>
+        <v>5.282</v>
       </c>
       <c r="V29" t="n">
-        <v>2.524</v>
+        <v>2.525</v>
       </c>
       <c r="W29" t="n">
-        <v>0.445</v>
+        <v>0.517</v>
       </c>
       <c r="X29" t="n">
-        <v>0.352</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="30">

--- a/data/live/BallparkPal_Pitchers_2026-04-12.xlsx
+++ b/data/live/BallparkPal_Pitchers_2026-04-12.xlsx
@@ -1306,46 +1306,46 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>24.332</v>
+        <v>24.26</v>
       </c>
       <c r="L10" t="n">
-        <v>6.221</v>
+        <v>6.184</v>
       </c>
       <c r="M10" t="n">
-        <v>0.451</v>
+        <v>0.419</v>
       </c>
       <c r="N10" t="n">
-        <v>0.177</v>
+        <v>0.187</v>
       </c>
       <c r="O10" t="n">
-        <v>0.454</v>
+        <v>0.481</v>
       </c>
       <c r="P10" t="n">
-        <v>0.625</v>
+        <v>0.618</v>
       </c>
       <c r="Q10" t="n">
-        <v>25.555</v>
+        <v>23.795</v>
       </c>
       <c r="R10" t="n">
-        <v>43.41</v>
+        <v>40.894</v>
       </c>
       <c r="S10" t="n">
-        <v>1.632</v>
+        <v>1.697</v>
       </c>
       <c r="T10" t="n">
-        <v>3.837</v>
+        <v>4.017</v>
       </c>
       <c r="U10" t="n">
-        <v>8.145</v>
+        <v>7.481</v>
       </c>
       <c r="V10" t="n">
-        <v>1.768</v>
+        <v>1.716</v>
       </c>
       <c r="W10" t="n">
-        <v>0.67</v>
+        <v>0.648</v>
       </c>
       <c r="X10" t="n">
-        <v>0.379</v>
+        <v>0.388</v>
       </c>
     </row>
     <row r="11">
@@ -1396,46 +1396,46 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>22.965</v>
+        <v>23.011</v>
       </c>
       <c r="L11" t="n">
-        <v>5.405</v>
+        <v>5.477</v>
       </c>
       <c r="M11" t="n">
-        <v>0.17</v>
+        <v>0.186</v>
       </c>
       <c r="N11" t="n">
-        <v>0.465</v>
+        <v>0.433</v>
       </c>
       <c r="O11" t="n">
-        <v>0.642</v>
+        <v>0.628</v>
       </c>
       <c r="P11" t="n">
-        <v>0.387</v>
+        <v>0.408</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.571</v>
+        <v>13.41</v>
       </c>
       <c r="R11" t="n">
-        <v>24.669</v>
+        <v>25.793</v>
       </c>
       <c r="S11" t="n">
-        <v>2.458</v>
+        <v>2.462</v>
       </c>
       <c r="T11" t="n">
-        <v>5.362</v>
+        <v>5.323</v>
       </c>
       <c r="U11" t="n">
-        <v>4.421</v>
+        <v>4.666</v>
       </c>
       <c r="V11" t="n">
-        <v>1.642</v>
+        <v>1.484</v>
       </c>
       <c r="W11" t="n">
-        <v>0.636</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>0.467</v>
+        <v>0.549</v>
       </c>
     </row>
     <row r="12">
@@ -1453,16 +1453,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>668678</v>
+        <v>647315</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zac Gallen</t>
+          <t>Zach Pop</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gallen</t>
+          <t>Pop</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1472,60 +1472,60 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>ARI</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="K12" t="n">
-        <v>23.085</v>
+        <v>4.186</v>
       </c>
       <c r="L12" t="n">
-        <v>5.409</v>
+        <v>0.947</v>
       </c>
       <c r="M12" t="n">
-        <v>0.282</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.328</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.632</v>
+        <v>0.542</v>
       </c>
       <c r="P12" t="n">
-        <v>0.395</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.516</v>
+        <v>1.644</v>
       </c>
       <c r="R12" t="n">
-        <v>24.733</v>
+        <v>3.415</v>
       </c>
       <c r="S12" t="n">
-        <v>2.408</v>
+        <v>0.453</v>
       </c>
       <c r="T12" t="n">
-        <v>4.804</v>
+        <v>1.036</v>
       </c>
       <c r="U12" t="n">
-        <v>4.153</v>
+        <v>0.644</v>
       </c>
       <c r="V12" t="n">
-        <v>2.327</v>
+        <v>0.414</v>
       </c>
       <c r="W12" t="n">
-        <v>0.68</v>
+        <v>0.099</v>
       </c>
       <c r="X12" t="n">
-        <v>0.511</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="13">
@@ -1543,16 +1543,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>691725</v>
+        <v>668678</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Zac Gallen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Painter</t>
+          <t>Gallen</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1562,60 +1562,60 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>ARI</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>ARI</t>
-        </is>
-      </c>
       <c r="K13" t="n">
-        <v>22.265</v>
+        <v>23.085</v>
       </c>
       <c r="L13" t="n">
-        <v>5.222</v>
+        <v>5.409</v>
       </c>
       <c r="M13" t="n">
-        <v>0.273</v>
+        <v>0.282</v>
       </c>
       <c r="N13" t="n">
-        <v>0.279</v>
+        <v>0.328</v>
       </c>
       <c r="O13" t="n">
-        <v>0.672</v>
+        <v>0.632</v>
       </c>
       <c r="P13" t="n">
-        <v>0.321</v>
+        <v>0.395</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.144</v>
+        <v>12.516</v>
       </c>
       <c r="R13" t="n">
-        <v>25.198</v>
+        <v>24.733</v>
       </c>
       <c r="S13" t="n">
-        <v>2.089</v>
+        <v>2.408</v>
       </c>
       <c r="T13" t="n">
-        <v>4.706</v>
+        <v>4.804</v>
       </c>
       <c r="U13" t="n">
-        <v>4.291</v>
+        <v>4.153</v>
       </c>
       <c r="V13" t="n">
-        <v>2.145</v>
+        <v>2.327</v>
       </c>
       <c r="W13" t="n">
-        <v>0.464</v>
+        <v>0.68</v>
       </c>
       <c r="X13" t="n">
-        <v>0.438</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="14">
@@ -2026,46 +2026,46 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>22.571</v>
+        <v>22.599</v>
       </c>
       <c r="L18" t="n">
-        <v>5.637</v>
+        <v>5.697</v>
       </c>
       <c r="M18" t="n">
-        <v>0.392</v>
+        <v>0.404</v>
       </c>
       <c r="N18" t="n">
-        <v>0.204</v>
+        <v>0.196</v>
       </c>
       <c r="O18" t="n">
-        <v>0.571</v>
+        <v>0.551</v>
       </c>
       <c r="P18" t="n">
-        <v>0.455</v>
+        <v>0.498</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.648</v>
+        <v>22.274</v>
       </c>
       <c r="R18" t="n">
-        <v>37.272</v>
+        <v>38.214</v>
       </c>
       <c r="S18" t="n">
-        <v>1.898</v>
+        <v>1.78</v>
       </c>
       <c r="T18" t="n">
-        <v>3.762</v>
+        <v>3.654</v>
       </c>
       <c r="U18" t="n">
-        <v>7.295</v>
+        <v>7.348</v>
       </c>
       <c r="V18" t="n">
-        <v>1.956</v>
+        <v>1.897</v>
       </c>
       <c r="W18" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="X18" t="n">
-        <v>0.539</v>
+        <v>0.577</v>
       </c>
     </row>
     <row r="19">
@@ -2116,46 +2116,46 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>19.462</v>
+        <v>19.541</v>
       </c>
       <c r="L19" t="n">
-        <v>4.402</v>
+        <v>4.46</v>
       </c>
       <c r="M19" t="n">
-        <v>0.112</v>
+        <v>0.11</v>
       </c>
       <c r="N19" t="n">
-        <v>0.366</v>
+        <v>0.383</v>
       </c>
       <c r="O19" t="n">
-        <v>0.876</v>
+        <v>0.865</v>
       </c>
       <c r="P19" t="n">
-        <v>0.101</v>
+        <v>0.105</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.090999999999999</v>
+        <v>9.426</v>
       </c>
       <c r="R19" t="n">
-        <v>18.231</v>
+        <v>18.636</v>
       </c>
       <c r="S19" t="n">
-        <v>2.23</v>
+        <v>2.187</v>
       </c>
       <c r="T19" t="n">
-        <v>3.831</v>
+        <v>3.885</v>
       </c>
       <c r="U19" t="n">
-        <v>3.546</v>
+        <v>3.58</v>
       </c>
       <c r="V19" t="n">
-        <v>2.66</v>
+        <v>2.505</v>
       </c>
       <c r="W19" t="n">
-        <v>0.59</v>
+        <v>0.599</v>
       </c>
       <c r="X19" t="n">
-        <v>0.409</v>
+        <v>0.346</v>
       </c>
     </row>
     <row r="20">
